--- a/data/trans_camb/P1428-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1428-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-2,97</t>
+          <t>-3,02</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,3</t>
+          <t>-5,51</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,14</t>
+          <t>-4,2</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 2,0</t>
+          <t>-5,25; 2,07</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 3,82</t>
+          <t>-3,92; 3,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 0,18</t>
+          <t>-6,94; -0,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,93; 0,04</t>
+          <t>-10,68; -0,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 1,14</t>
+          <t>-10,46; 0,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,78; -0,47</t>
+          <t>-10,65; -0,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,99; -0,41</t>
+          <t>-6,75; 0,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,5; 0,78</t>
+          <t>-5,93; 1,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,27; -1,27</t>
+          <t>-7,24; -1,52</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-50,13%</t>
+          <t>-51,07%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-40,16%</t>
+          <t>-41,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-43,7%</t>
+          <t>-44,26%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-69,96; 60,62</t>
+          <t>-69,22; 55,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-51,97; 91,58</t>
+          <t>-51,75; 99,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-78,15; 15,65</t>
+          <t>-80,93; 1,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-66,81; 4,45</t>
+          <t>-65,54; 1,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,46; 10,7</t>
+          <t>-61,8; 11,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-59,37; -3,1</t>
+          <t>-62,81; -4,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-59,71; -2,96</t>
+          <t>-60,11; 2,67</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 8,86</t>
+          <t>-50,56; 16,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-61,06; -14,96</t>
+          <t>-62,29; -19,72</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-0,7</t>
+          <t>-0,71</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-9,17</t>
+          <t>-9,35</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,04</t>
+          <t>-5,09</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 0,9</t>
+          <t>-4,06; 0,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 0,99</t>
+          <t>-3,9; 0,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,82</t>
+          <t>-3,26; 1,8</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,67; -4,76</t>
+          <t>-13,1; -4,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,24; -4,68</t>
+          <t>-13,64; -5,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,19; -5,77</t>
+          <t>-13,35; -5,2</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,81; -2,7</t>
+          <t>-7,78; -2,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,0; -2,79</t>
+          <t>-7,69; -2,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,39; -2,34</t>
+          <t>-7,44; -2,76</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-15,41%</t>
+          <t>-15,66%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-49,97%</t>
+          <t>-50,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-43,68%</t>
+          <t>-44,09%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-69,91; 40,53</t>
+          <t>-70,55; 30,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-67,84; 34,08</t>
+          <t>-66,03; 34,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-53,24; 60,59</t>
+          <t>-56,47; 55,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-63,51; -29,1</t>
+          <t>-63,92; -29,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,86; -28,95</t>
+          <t>-64,88; -30,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,36; -35,12</t>
+          <t>-63,34; -33,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,73; -24,95</t>
+          <t>-61,0; -28,61</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,9; -26,61</t>
+          <t>-59,23; -24,53</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-56,61; -23,14</t>
+          <t>-57,87; -26,28</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>2,32</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,45</t>
+          <t>-2,5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,02</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 7,22</t>
+          <t>0,11; 6,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 3,02</t>
+          <t>-2,58; 3,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 5,5</t>
+          <t>-0,44; 5,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 1,47</t>
+          <t>-9,21; 1,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,76; -5,72</t>
+          <t>-15,97; -6,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 2,55</t>
+          <t>-7,6; 2,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 3,36</t>
+          <t>-3,56; 3,46</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,34; -2,46</t>
+          <t>-8,32; -2,45</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 2,94</t>
+          <t>-3,23; 2,88</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-13,29%</t>
+          <t>-13,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 339,68</t>
+          <t>-4,0; 315,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-54,72; 124,44</t>
+          <t>-54,27; 145,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,95; 239,72</t>
+          <t>-12,72; 254,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-45,09; 9,58</t>
+          <t>-44,8; 12,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-72,89; -34,24</t>
+          <t>-74,24; -36,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-35,88; 16,34</t>
+          <t>-34,24; 18,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-27,79; 35,67</t>
+          <t>-27,65; 35,92</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-63,61; -24,51</t>
+          <t>-65,09; -26,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-24,26; 30,76</t>
+          <t>-24,87; 29,88</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,62</t>
+          <t>1,87</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>5,2</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>3,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,21; 1,2</t>
+          <t>-5,47; 1,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 1,04</t>
+          <t>-5,82; 0,88</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 6,76</t>
+          <t>-2,1; 5,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-10,4; -0,58</t>
+          <t>-10,78; -1,01</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 0,91</t>
+          <t>-8,9; 1,57</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 8,07</t>
+          <t>-0,4; 10,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -1,1</t>
+          <t>-7,18; -0,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,57; -0,31</t>
+          <t>-6,55; -0,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 6,36</t>
+          <t>0,8; 7,09</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-64,35; 29,89</t>
+          <t>-63,68; 26,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-66,73; 25,86</t>
+          <t>-67,36; 26,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 133,61</t>
+          <t>-24,42; 111,85</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-51,92; -3,09</t>
+          <t>-53,61; -6,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-47,19; 6,47</t>
+          <t>-46,27; 11,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-36,08; 53,14</t>
+          <t>-2,29; 75,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-52,1; -9,6</t>
+          <t>-51,34; -6,91</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-46,96; -2,81</t>
+          <t>-47,42; 0,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-18,28; 59,73</t>
+          <t>5,16; 69,3</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,08</t>
+          <t>-2,24</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,69</t>
+          <t>-2,43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-2,1</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 2,78</t>
+          <t>-7,67; 2,14</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,2; -0,33</t>
+          <t>-9,49; -0,71</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 2,2</t>
+          <t>-6,91; 1,81</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 3,09</t>
+          <t>-11,57; 3,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-17,12; -2,89</t>
+          <t>-17,87; -3,84</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 5,04</t>
+          <t>-9,56; 3,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 1,02</t>
+          <t>-8,25; 1,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,78; -3,59</t>
+          <t>-11,72; -3,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 2,46</t>
+          <t>-6,34; 1,53</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-27,66%</t>
+          <t>-29,74%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-8,34%</t>
+          <t>-11,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-10,45%</t>
+          <t>-15,03%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-71,32; 70,45</t>
+          <t>-75,15; 48,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-87,8; 15,61</t>
+          <t>-86,13; -0,95</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-62,67; 56,37</t>
+          <t>-65,05; 41,98</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-50,44; 19,94</t>
+          <t>-48,89; 20,58</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-71,21; -15,82</t>
+          <t>-72,21; -19,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 32,95</t>
+          <t>-36,32; 24,48</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-48,71; 10,26</t>
+          <t>-49,17; 11,09</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-70,32; -29,51</t>
+          <t>-71,64; -23,66</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 21,1</t>
+          <t>-36,07; 13,48</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,58</t>
+          <t>1,46</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,17; 9,26</t>
+          <t>-0,05; 9,45</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 1,62</t>
+          <t>-6,37; 1,72</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 5,38</t>
+          <t>-2,07; 5,97</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 9,72</t>
+          <t>-3,58; 9,74</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,7; 1,56</t>
+          <t>-10,32; 2,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 6,78</t>
+          <t>-4,43; 6,57</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,05; 7,92</t>
+          <t>0,29; 8,08</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 0,62</t>
+          <t>-6,77; 0,3</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 4,84</t>
+          <t>-1,82; 4,72</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 186,83</t>
+          <t>-1,13; 209,34</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-68,87; 43,01</t>
+          <t>-70,98; 41,17</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 117,66</t>
+          <t>-24,86; 139,63</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-18,62; 70,44</t>
+          <t>-17,17; 65,65</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-51,76; 10,99</t>
+          <t>-51,5; 15,74</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 49,11</t>
+          <t>-21,17; 48,89</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 77,16</t>
+          <t>1,04; 79,21</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 6,1</t>
+          <t>-48,1; 5,98</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 49,23</t>
+          <t>-13,06; 49,12</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-1,7</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>1,1</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>12,13</t>
+          <t>-0,19</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 0,96</t>
+          <t>-5,11; 0,93</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-7,17; -1,88</t>
+          <t>-7,13; -1,72</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 1,42</t>
+          <t>-4,68; 1,26</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 4,69</t>
+          <t>-3,66; 4,58</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-10,73; -2,97</t>
+          <t>-10,08; -2,86</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 52,52</t>
+          <t>-2,65; 4,91</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 1,98</t>
+          <t>-2,95; 2,17</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-7,83; -3,54</t>
+          <t>-7,81; -3,25</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 41,03</t>
+          <t>-2,83; 2,1</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>-18,22%</t>
+          <t>-20,99%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>144,74%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>105,66%</t>
+          <t>-1,69%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-50,79; 15,21</t>
+          <t>-51,95; 16,1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-72,57; -27,29</t>
+          <t>-73,14; -25,9</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-44,33; 22,01</t>
+          <t>-47,03; 21,54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-19,04; 37,08</t>
+          <t>-22,09; 36,44</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-61,73; -21,69</t>
+          <t>-61,03; -21,8</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 420,5</t>
+          <t>-15,39; 39,71</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-23,55; 19,69</t>
+          <t>-22,54; 21,94</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-61,33; -33,37</t>
+          <t>-60,63; -31,46</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 411,38</t>
+          <t>-21,45; 21,33</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-8,3</t>
+          <t>-7,48</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-7,44</t>
+          <t>-8,34</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-8,69</t>
+          <t>-7,95</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-9,98; -4,6</t>
+          <t>-10,04; -4,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-10,43; -5,39</t>
+          <t>-10,71; -5,37</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-10,95; -5,69</t>
+          <t>-10,19; -5,04</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-14,71; -7,53</t>
+          <t>-14,73; -7,98</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-15,44; -8,24</t>
+          <t>-15,71; -8,55</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-11,12; -3,63</t>
+          <t>-11,97; -4,81</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-11,69; -7,08</t>
+          <t>-11,8; -7,0</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-12,38; -7,96</t>
+          <t>-12,35; -7,8</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-12,3; -6,17</t>
+          <t>-10,11; -5,67</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-77,71%</t>
+          <t>-70,04%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-36,44%</t>
+          <t>-40,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-55,4%</t>
+          <t>-50,69%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-80,13; -49,16</t>
+          <t>-80,87; -49,23</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-85,59; -57,48</t>
+          <t>-85,91; -58,24</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-91,24; -64,25</t>
+          <t>-80,28; -54,62</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-65,63; -40,89</t>
+          <t>-66,28; -43,67</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-69,42; -45,3</t>
+          <t>-69,75; -45,16</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-48,46; -18,31</t>
+          <t>-52,23; -25,78</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-68,5; -49,22</t>
+          <t>-68,57; -48,94</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-72,4; -53,33</t>
+          <t>-72,44; -54,48</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-72,26; -41,84</t>
+          <t>-58,78; -39,62</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>-3,27</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-2,58</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-3,29; -0,94</t>
+          <t>-3,21; -0,77</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,63; -2,48</t>
+          <t>-4,76; -2,62</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,98</t>
+          <t>-3,09; -0,86</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-7,0; -3,59</t>
+          <t>-6,89; -3,51</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -6,5</t>
+          <t>-10,08; -6,77</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 18,52</t>
+          <t>-4,93; -1,73</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-4,76; -2,52</t>
+          <t>-4,73; -2,61</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -5,01</t>
+          <t>-6,93; -4,98</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 10,99</t>
+          <t>-3,61; -1,63</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-30,36%</t>
+          <t>-27,25%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>-18,53%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-1,99%</t>
+          <t>-20,59%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-41,41; -13,97</t>
+          <t>-41,1; -12,03</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-59,58; -38,43</t>
+          <t>-60,02; -39,03</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -14,87</t>
+          <t>-39,56; -13,39</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-37,61; -21,33</t>
+          <t>-36,84; -20,64</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-53,52; -39,36</t>
+          <t>-53,63; -39,71</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 103,97</t>
+          <t>-26,34; -10,26</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-36,34; -20,82</t>
+          <t>-36,46; -21,67</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-53,21; -41,94</t>
+          <t>-52,94; -41,1</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 87,72</t>
+          <t>-27,49; -13,63</t>
         </is>
       </c>
     </row>
